--- a/exports/GAIL_full_report.xlsx
+++ b/exports/GAIL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.78</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.38541666666</v>
+        <v>44585.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>82.93000000000001</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>82.62779249244446</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.11</v>
+        <v>-0.63</v>
       </c>
       <c r="L2" t="n">
-        <v>0.91</v>
+        <v>1.81</v>
       </c>
       <c r="M2" t="n">
         <v>1.88</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>5.49</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44595.55208333334</v>
+        <v>44596.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>86.56999999999999</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>86.83637774502282</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.16</v>
+        <v>-5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>6.71</v>
+        <v>8.75</v>
       </c>
       <c r="M3" t="n">
-        <v>0.95</v>
+        <v>1.84</v>
       </c>
       <c r="N3" t="n">
         <v>2.72</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>5.37</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.38541666666</v>
+        <v>44603.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>82.73999999999999</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>82.50089764659654</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.09</v>
+        <v>-5.57</v>
       </c>
       <c r="L4" t="n">
-        <v>5.62</v>
+        <v>5.84</v>
       </c>
       <c r="M4" t="n">
         <v>0.61</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>6.08</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>78.91</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>83.31506611182047</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>4.14</v>
+        <v>-1.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="M5" t="n">
         <v>1.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>7.82</v>
       </c>
       <c r="O5" t="n">
         <v>-0.84</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>12.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>90.93000000000001</v>
+        <v>86.81</v>
       </c>
       <c r="I6" t="n">
         <v>86.93223592995815</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>9.09</v>
+        <v>4.15</v>
       </c>
       <c r="L6" t="n">
         <v>6.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.39</v>
+        <v>4.38</v>
       </c>
       <c r="O6" t="n">
         <v>7.82</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.52</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44650.38541666666</v>
+        <v>44650.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>89.75</v>
+        <v>90.45</v>
       </c>
       <c r="I7" t="n">
         <v>90.35870019870787</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.39</v>
+        <v>-4.19</v>
       </c>
       <c r="L7" t="n">
         <v>6.24</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>5.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44671.55208333334</v>
+        <v>44672.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>97.98</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>96.4553930932738</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>8.33</v>
+        <v>5.63</v>
       </c>
       <c r="L8" t="n">
         <v>1.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="N8" t="n">
         <v>1.92</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.29</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44757.38541666666</v>
+        <v>44757.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>82.28</v>
+        <v>82.37</v>
       </c>
       <c r="I9" t="n">
         <v>82.2835284666178</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>85</v>
+        <v>85.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>13.88</v>
+        <v>13.78</v>
       </c>
       <c r="L9" t="n">
         <v>2.65</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.37</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44775.55208333334</v>
+        <v>44776.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>83.02</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>82.50524615895398</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.79</v>
+        <v>-1.14</v>
       </c>
       <c r="L10" t="n">
         <v>2.39</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.08</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>78.44</v>
+        <v>79.47</v>
       </c>
       <c r="I11" t="n">
         <v>79.39784368339335</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>3.67</v>
+        <v>2.41</v>
       </c>
       <c r="L11" t="n">
         <v>2.64</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>4.55</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44824.55208333334</v>
+        <v>44825.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>79.70999999999999</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>79.01340320124183</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3</v>
+        <v>-1.94</v>
       </c>
       <c r="L12" t="n">
-        <v>0.99</v>
+        <v>2.35</v>
       </c>
       <c r="M12" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="O12" t="n">
         <v>1.67</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.41</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44841.55208333334</v>
+        <v>44844.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>76.25</v>
+        <v>77.7</v>
       </c>
       <c r="I13" t="n">
         <v>77.61603653016219</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>2.16</v>
+        <v>0.3</v>
       </c>
       <c r="L13" t="n">
         <v>2.4</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44879.38541666666</v>
+        <v>44879.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>77.47</v>
+        <v>77.14</v>
       </c>
       <c r="I14" t="n">
         <v>77.17620218638923</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3</v>
+        <v>-0.72</v>
       </c>
       <c r="L14" t="n">
         <v>5.42</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>4.11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44888.55208333334</v>
+        <v>44889.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>79.66</v>
+        <v>80.83</v>
       </c>
       <c r="I15" t="n">
         <v>80.31140337273079</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.27</v>
+        <v>-4.78</v>
       </c>
       <c r="L15" t="n">
-        <v>4.23</v>
+        <v>5.21</v>
       </c>
       <c r="M15" t="n">
         <v>0.77</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.4</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44904.38541666666</v>
+        <v>44904.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>81.06</v>
+        <v>79.75</v>
       </c>
       <c r="I16" t="n">
         <v>80.0495312491426</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>0.28</v>
+        <v>-1.34</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
         <v>0.22</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>4.23</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44908.55208333334</v>
+        <v>44909.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>81.91</v>
+        <v>84</v>
       </c>
       <c r="I17" t="n">
         <v>83.12080305669576</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.71</v>
+        <v>-5.33</v>
       </c>
       <c r="L17" t="n">
-        <v>3.64</v>
+        <v>5.58</v>
       </c>
       <c r="M17" t="n">
         <v>0.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="O17" t="n">
         <v>-2.01</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>5.38</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>82.7</v>
+        <v>80.83</v>
       </c>
       <c r="I18" t="n">
         <v>82.67102943591723</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.55</v>
+        <v>-3.77</v>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>4.44</v>
       </c>
       <c r="M18" t="n">
-        <v>0.43</v>
+        <v>1.14</v>
       </c>
       <c r="N18" t="n">
         <v>3.2</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.64</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>85.22</v>
+        <v>85.31</v>
       </c>
       <c r="I19" t="n">
         <v>85.24107832505229</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.43</v>
+        <v>-5.54</v>
       </c>
       <c r="L19" t="n">
-        <v>6.14</v>
+        <v>6.24</v>
       </c>
       <c r="M19" t="n">
         <v>0.77</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>89.47</v>
+        <v>86.81</v>
       </c>
       <c r="I20" t="n">
         <v>87.15873016342923</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K20" t="n">
-        <v>4.88</v>
+        <v>1.76</v>
       </c>
       <c r="L20" t="n">
         <v>1.81</v>
@@ -1581,7 +1820,7 @@
         <v>0.82</v>
       </c>
       <c r="N20" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="O20" t="n">
         <v>0.22</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.06</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>84.15000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="I21" t="n">
         <v>86.26994731677145</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>3.06</v>
+        <v>0.22</v>
       </c>
       <c r="L21" t="n">
         <v>4.52</v>
       </c>
       <c r="M21" t="n">
-        <v>0.77</v>
+        <v>1.65</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="O21" t="n">
         <v>-1.88</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5.14</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45005.55208333334</v>
+        <v>45006.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>97.65000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>93.59923784954172</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K22" t="n">
-        <v>12.73</v>
+        <v>7.28</v>
       </c>
       <c r="L22" t="n">
         <v>2.04</v>
       </c>
       <c r="M22" t="n">
-        <v>0.92</v>
+        <v>3.83</v>
       </c>
       <c r="N22" t="n">
-        <v>2.03</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>2.94</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.59</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45033.38541666666</v>
+        <v>45033.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>96.72</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>97.21738974834275</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.08</v>
+        <v>-5.53</v>
       </c>
       <c r="L23" t="n">
         <v>6.09</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.3</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>97.05</v>
+        <v>94.05</v>
       </c>
       <c r="I24" t="n">
         <v>94.24941406296672</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.04</v>
+        <v>-4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>1.19</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
         <v>2.19</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45061.38541666666</v>
+        <v>45061.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>97.28</v>
+        <v>99.42</v>
       </c>
       <c r="I25" t="n">
         <v>97.86572626195334</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.43</v>
+        <v>-5.71</v>
       </c>
       <c r="L25" t="n">
-        <v>4.03</v>
+        <v>5.76</v>
       </c>
       <c r="M25" t="n">
         <v>0.78</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.95</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>97.28</v>
+        <v>93.86</v>
       </c>
       <c r="I26" t="n">
         <v>96.50849139286889</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.15</v>
+        <v>-5.59</v>
       </c>
       <c r="L26" t="n">
-        <v>3.29</v>
+        <v>6.67</v>
       </c>
       <c r="M26" t="n">
         <v>0.04</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.92</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45093.55208333334</v>
+        <v>45096.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>95.31</v>
+        <v>95.87</v>
       </c>
       <c r="I27" t="n">
         <v>95.62621491434251</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.54</v>
+        <v>-2.14</v>
       </c>
       <c r="L27" t="n">
         <v>3.7</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.66</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45099.38541666666</v>
+        <v>45099.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>93.77</v>
+        <v>92.23</v>
       </c>
       <c r="I28" t="n">
         <v>93.01769588261386</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.19</v>
+        <v>-3.8</v>
       </c>
       <c r="L28" t="n">
-        <v>2.63</v>
+        <v>3.99</v>
       </c>
       <c r="M28" t="n">
         <v>0.14</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>4.64</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45111.55208333334</v>
+        <v>45112.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>94.23999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="I29" t="n">
         <v>94.90104713878733</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.18</v>
+        <v>-3.34</v>
       </c>
       <c r="L29" t="n">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="M29" t="n">
         <v>0.59</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.95</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>102.5</v>
+        <v>102.18</v>
       </c>
       <c r="I30" t="n">
         <v>102.2718098391469</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K30" t="n">
-        <v>7.54</v>
+        <v>7.21</v>
       </c>
       <c r="L30" t="n">
         <v>1.37</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>104.1</v>
+        <v>105.22</v>
       </c>
       <c r="I31" t="n">
         <v>104.8246905755958</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.88</v>
+        <v>-2.98</v>
       </c>
       <c r="L31" t="n">
         <v>3.89</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.44</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>110.45</v>
+        <v>108.54</v>
       </c>
       <c r="I32" t="n">
         <v>108.9335723044199</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K32" t="n">
-        <v>4.97</v>
+        <v>3.16</v>
       </c>
       <c r="L32" t="n">
         <v>3.64</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>7.42</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>110.21</v>
+        <v>113.76</v>
       </c>
       <c r="I33" t="n">
         <v>113.1518158856566</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.54</v>
+        <v>-4.81</v>
       </c>
       <c r="L33" t="n">
-        <v>3.79</v>
+        <v>5.59</v>
       </c>
       <c r="M33" t="n">
         <v>0.67</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>5.48</v>
       </c>
       <c r="O33" t="n">
         <v>-1.9</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.81</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>115.5</v>
+        <v>110.68</v>
       </c>
       <c r="I34" t="n">
         <v>111.8899520092276</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>1.53</v>
+        <v>-2.71</v>
       </c>
       <c r="L34" t="n">
         <v>3.03</v>
@@ -2379,7 +2786,7 @@
         <v>0.92</v>
       </c>
       <c r="N34" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>5.48</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.77</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45239.55208333334</v>
+        <v>45240.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>110.73</v>
+        <v>111.9</v>
       </c>
       <c r="I35" t="n">
         <v>111.6400856179652</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.05</v>
+        <v>-1.1</v>
       </c>
       <c r="L35" t="n">
         <v>4.52</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>129</v>
+        <v>123.3</v>
       </c>
       <c r="I36" t="n">
         <v>124.5356751800026</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>15.28</v>
+        <v>10.19</v>
       </c>
       <c r="L36" t="n">
         <v>1.97</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>9.48</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45281.55208333334</v>
+        <v>45282.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>126.61</v>
+        <v>136.48</v>
       </c>
       <c r="I37" t="n">
         <v>133.643936402298</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.68</v>
+        <v>-10.69</v>
       </c>
       <c r="L37" t="n">
-        <v>4.7</v>
+        <v>11.37</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="N37" t="n">
-        <v>2.68</v>
+        <v>7.65</v>
       </c>
       <c r="O37" t="n">
         <v>-5.21</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.98</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>159.46</v>
+        <v>157.55</v>
       </c>
       <c r="I38" t="n">
         <v>157.8121218021015</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>16.84</v>
+        <v>15.44</v>
       </c>
       <c r="L38" t="n">
         <v>7.16</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>9.43</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45336.55208333334</v>
+        <v>45337.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>164.79</v>
+        <v>172.69</v>
       </c>
       <c r="I39" t="n">
         <v>172.0031021088091</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.6</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>4.83</v>
+        <v>9.66</v>
       </c>
       <c r="M39" t="n">
         <v>0.41</v>
       </c>
       <c r="N39" t="n">
-        <v>3.46</v>
+        <v>4.28</v>
       </c>
       <c r="O39" t="n">
         <v>-2.68</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.88</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>171.47</v>
+        <v>167.92</v>
       </c>
       <c r="I40" t="n">
         <v>170.0949509583012</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.71</v>
+        <v>-2.76</v>
       </c>
       <c r="L40" t="n">
         <v>4.96</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>171.1</v>
+        <v>178.48</v>
       </c>
       <c r="I41" t="n">
         <v>171.631042268502</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.89</v>
+        <v>-6.29</v>
       </c>
       <c r="L41" t="n">
-        <v>2.72</v>
+        <v>6.71</v>
       </c>
       <c r="M41" t="n">
         <v>1.18</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.67</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>190.53</v>
+        <v>184.03</v>
       </c>
       <c r="I42" t="n">
         <v>186.1452060823815</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K42" t="n">
-        <v>6.75</v>
+        <v>3.11</v>
       </c>
       <c r="L42" t="n">
         <v>4.5</v>
@@ -2835,7 +3338,7 @@
         <v>2.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.91</v>
+        <v>2.97</v>
       </c>
       <c r="O42" t="n">
         <v>3.24</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>191.56</v>
+        <v>194.97</v>
       </c>
       <c r="I43" t="n">
         <v>191.6211475036798</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.09</v>
+        <v>-5.94</v>
       </c>
       <c r="L43" t="n">
-        <v>4.24</v>
+        <v>6.81</v>
       </c>
       <c r="M43" t="n">
         <v>1.01</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.9</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>214.97</v>
+        <v>182.64</v>
       </c>
       <c r="I44" t="n">
         <v>196.426489861191</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
-        <v>10.26</v>
+        <v>-6.32</v>
       </c>
       <c r="L44" t="n">
-        <v>5.15</v>
+        <v>16.84</v>
       </c>
       <c r="M44" t="n">
         <v>0.85</v>
       </c>
       <c r="N44" t="n">
-        <v>1.9</v>
+        <v>15.89</v>
       </c>
       <c r="O44" t="n">
         <v>1.78</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>20.26</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45481.38541666666</v>
+        <v>45481.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>207.36</v>
+        <v>215.71</v>
       </c>
       <c r="I45" t="n">
         <v>209.6251176711651</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K45" t="n">
-        <v>-13.53</v>
+        <v>-18.11</v>
       </c>
       <c r="L45" t="n">
-        <v>17.9</v>
+        <v>18.41</v>
       </c>
       <c r="M45" t="n">
         <v>3.27</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.4</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>214.06</v>
+        <v>207.36</v>
       </c>
       <c r="I46" t="n">
         <v>207.5680131231105</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.76</v>
+        <v>-3.87</v>
       </c>
       <c r="L46" t="n">
-        <v>4.76</v>
+        <v>4.94</v>
       </c>
       <c r="M46" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="O46" t="n">
         <v>3.4</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>7.85</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45503.55208333334</v>
+        <v>45504.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>217.91</v>
+        <v>224.45</v>
       </c>
       <c r="I47" t="n">
         <v>221.0305761114512</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.09</v>
+        <v>-8.24</v>
       </c>
       <c r="L47" t="n">
-        <v>6.53</v>
+        <v>11</v>
       </c>
       <c r="M47" t="n">
-        <v>1.32</v>
+        <v>3.35</v>
       </c>
       <c r="N47" t="n">
-        <v>2.38</v>
+        <v>3.52</v>
       </c>
       <c r="O47" t="n">
         <v>-4.3</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.74</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>221.13</v>
+        <v>210.05</v>
       </c>
       <c r="I48" t="n">
         <v>211.5689431266292</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.48</v>
+        <v>-6.42</v>
       </c>
       <c r="L48" t="n">
-        <v>3.37</v>
+        <v>7.99</v>
       </c>
       <c r="M48" t="n">
-        <v>1.09</v>
+        <v>2.81</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>5.28</v>
       </c>
       <c r="O48" t="n">
         <v>3.52</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.66</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45558.55208333334</v>
+        <v>45559.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>206.37</v>
+        <v>208.25</v>
       </c>
       <c r="I49" t="n">
         <v>207.1524198773477</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K49" t="n">
-        <v>1.75</v>
+        <v>0.86</v>
       </c>
       <c r="L49" t="n">
         <v>7.5</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.84</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>215.3</v>
+        <v>208.67</v>
       </c>
       <c r="I50" t="n">
         <v>212.5345809079851</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K50" t="n">
-        <v>3.39</v>
+        <v>0.2</v>
       </c>
       <c r="L50" t="n">
         <v>1.47</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.42</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>183.9</v>
+        <v>194.64</v>
       </c>
       <c r="I51" t="n">
         <v>192.509374879478</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K51" t="n">
-        <v>11.87</v>
+        <v>6.72</v>
       </c>
       <c r="L51" t="n">
         <v>5.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="N51" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="O51" t="n">
         <v>-2.61</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.58</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>189.69</v>
+        <v>182.88</v>
       </c>
       <c r="I52" t="n">
         <v>184.1332776774171</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.54</v>
+        <v>-6.04</v>
       </c>
       <c r="L52" t="n">
-        <v>3.5</v>
+        <v>6.19</v>
       </c>
       <c r="M52" t="n">
         <v>1.07</v>
       </c>
       <c r="N52" t="n">
-        <v>3.16</v>
+        <v>4.36</v>
       </c>
       <c r="O52" t="n">
         <v>6.2</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>10.26</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>180.16</v>
+        <v>185.68</v>
       </c>
       <c r="I53" t="n">
         <v>185.5328405484275</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K53" t="n">
-        <v>1.49</v>
+        <v>-1.53</v>
       </c>
       <c r="L53" t="n">
         <v>4.84</v>
       </c>
       <c r="M53" t="n">
-        <v>0.59</v>
+        <v>2.39</v>
       </c>
       <c r="N53" t="n">
-        <v>2.13</v>
+        <v>3.37</v>
       </c>
       <c r="O53" t="n">
         <v>-4.36</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.82</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>190.23</v>
+        <v>188.02</v>
       </c>
       <c r="I54" t="n">
         <v>188.2082142999804</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K54" t="n">
-        <v>2.45</v>
+        <v>1.26</v>
       </c>
       <c r="L54" t="n">
         <v>3.12</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.27</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45688.38541666666</v>
+        <v>45688.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>164.65</v>
+        <v>165.58</v>
       </c>
       <c r="I55" t="n">
         <v>165.2637242446834</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>12.43</v>
+        <v>11.93</v>
       </c>
       <c r="L55" t="n">
         <v>1.88</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.77</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>162.86</v>
+        <v>156.06</v>
       </c>
       <c r="I56" t="n">
         <v>157.6948174055245</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.64</v>
+        <v>-5.75</v>
       </c>
       <c r="L56" t="n">
-        <v>2.33</v>
+        <v>5.76</v>
       </c>
       <c r="M56" t="n">
         <v>0.8</v>
       </c>
       <c r="N56" t="n">
-        <v>1.9</v>
+        <v>3.86</v>
       </c>
       <c r="O56" t="n">
         <v>6.43</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45734.38541666666</v>
+        <v>45734.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>156.31</v>
+        <v>159.29</v>
       </c>
       <c r="I57" t="n">
         <v>158.4625174714674</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.16</v>
+        <v>-2.07</v>
       </c>
       <c r="L57" t="n">
         <v>4.7</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.72</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>171.65</v>
+        <v>160.62</v>
       </c>
       <c r="I58" t="n">
         <v>168.5114447000637</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>7.76</v>
+        <v>0.83</v>
       </c>
       <c r="L58" t="n">
-        <v>1.94</v>
+        <v>2.83</v>
       </c>
       <c r="M58" t="n">
-        <v>2.2</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N58" t="n">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="O58" t="n">
         <v>4.69</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>166.74</v>
+        <v>174.96</v>
       </c>
       <c r="I59" t="n">
         <v>174.4984049190594</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.81</v>
+        <v>-8.93</v>
       </c>
       <c r="L59" t="n">
-        <v>7.13</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="N59" t="n">
-        <v>1.8</v>
+        <v>4.02</v>
       </c>
       <c r="O59" t="n">
         <v>-3.79</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.08</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>176.98</v>
+        <v>176.22</v>
       </c>
       <c r="I60" t="n">
         <v>176.5731830534831</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K60" t="n">
-        <v>1.15</v>
+        <v>0.72</v>
       </c>
       <c r="L60" t="n">
         <v>3.07</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.24</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45803.38541666666</v>
+        <v>45803.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>186.99</v>
+        <v>187.21</v>
       </c>
       <c r="I61" t="n">
         <v>187.2074545320577</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.11</v>
+        <v>-6.24</v>
       </c>
       <c r="L61" t="n">
         <v>7.13</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>4.51</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>186.26</v>
+        <v>183.63</v>
       </c>
       <c r="I62" t="n">
         <v>184.8104579897914</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.51</v>
+        <v>-1.91</v>
       </c>
       <c r="L62" t="n">
-        <v>3.49</v>
+        <v>4.08</v>
       </c>
       <c r="M62" t="n">
-        <v>0.13</v>
+        <v>1.07</v>
       </c>
       <c r="N62" t="n">
         <v>4.01</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>5.24</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45840.55208333334</v>
+        <v>45841.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>184.64</v>
+        <v>186.97</v>
       </c>
       <c r="I63" t="n">
         <v>185.3593209963403</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.55</v>
+        <v>-1.82</v>
       </c>
       <c r="L63" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="M63" t="n">
         <v>1.21</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>4.61</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>187.25</v>
+        <v>180.52</v>
       </c>
       <c r="I64" t="n">
         <v>181.0266883519101</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>0.15</v>
+        <v>-3.45</v>
       </c>
       <c r="L64" t="n">
-        <v>1.06</v>
+        <v>3.58</v>
       </c>
       <c r="M64" t="n">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="N64" t="n">
-        <v>0.08</v>
+        <v>4.19</v>
       </c>
       <c r="O64" t="n">
         <v>1.19</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.27</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>169.87</v>
+        <v>172.07</v>
       </c>
       <c r="I65" t="n">
         <v>170.0656549063237</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K65" t="n">
-        <v>5.9</v>
+        <v>4.68</v>
       </c>
       <c r="L65" t="n">
         <v>3.52</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>3.74</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>167.85</v>
+        <v>166.45</v>
       </c>
       <c r="I66" t="n">
         <v>166.8536873902168</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.45</v>
+        <v>-3.27</v>
       </c>
       <c r="L66" t="n">
-        <v>2.58</v>
+        <v>3.63</v>
       </c>
       <c r="M66" t="n">
         <v>0.72</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>3.79</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>170.68</v>
+        <v>174.56</v>
       </c>
       <c r="I67" t="n">
         <v>171.6754987826902</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.54</v>
+        <v>-4.87</v>
       </c>
       <c r="L67" t="n">
-        <v>2.64</v>
+        <v>5.14</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="N67" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
         <v>-2.25</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4.82</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45908.38541666666</v>
+        <v>45908.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>167.77</v>
+        <v>167.28</v>
       </c>
       <c r="I68" t="n">
         <v>167.7420868377569</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.89</v>
+        <v>-4.17</v>
       </c>
       <c r="L68" t="n">
-        <v>4.16</v>
+        <v>4.43</v>
       </c>
       <c r="M68" t="n">
         <v>0.07000000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>3.75</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>169.48</v>
+        <v>173.64</v>
       </c>
       <c r="I69" t="n">
         <v>173.4880800760057</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.32</v>
+        <v>-3.8</v>
       </c>
       <c r="L69" t="n">
-        <v>1.33</v>
+        <v>3.89</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="N69" t="n">
-        <v>0.78</v>
+        <v>2.45</v>
       </c>
       <c r="O69" t="n">
         <v>-0.8100000000000001</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.52</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>171.26</v>
+        <v>170.68</v>
       </c>
       <c r="I70" t="n">
         <v>170.7635820823986</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.37</v>
+        <v>-1.7</v>
       </c>
       <c r="L70" t="n">
         <v>2.1</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>3.29</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>171.38</v>
+        <v>172.74</v>
       </c>
       <c r="I71" t="n">
         <v>172.5486653699803</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.41</v>
+        <v>-1.21</v>
       </c>
       <c r="L71" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="M71" t="n">
         <v>0.43</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>3.45</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>178.54</v>
+        <v>169.85</v>
       </c>
       <c r="I72" t="n">
         <v>173.8037039310498</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K72" t="n">
-        <v>3.36</v>
+        <v>-1.67</v>
       </c>
       <c r="L72" t="n">
-        <v>2.61</v>
+        <v>3.55</v>
       </c>
       <c r="M72" t="n">
-        <v>0.68</v>
+        <v>6.46</v>
       </c>
       <c r="N72" t="n">
-        <v>2.71</v>
+        <v>4.25</v>
       </c>
       <c r="O72" t="n">
         <v>1.83</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.71</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>166.46</v>
+        <v>170.04</v>
       </c>
       <c r="I73" t="n">
         <v>168.1265745899089</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>-0.11</v>
       </c>
       <c r="L73" t="n">
         <v>1.31</v>
@@ -4602,7 +5477,7 @@
         <v>0.74</v>
       </c>
       <c r="N73" t="n">
-        <v>1.37</v>
+        <v>2.23</v>
       </c>
       <c r="O73" t="n">
         <v>-4.25</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>3.96</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46028.38541666666</v>
+        <v>46028.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>165.94</v>
+        <v>163.88</v>
       </c>
       <c r="I74" t="n">
         <v>165.4543939917428</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.41</v>
+        <v>-3.62</v>
       </c>
       <c r="L74" t="n">
-        <v>2.89</v>
+        <v>3.7</v>
       </c>
       <c r="M74" t="n">
         <v>0.06</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>3.92</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46050.38541666666</v>
+        <v>46050.55208333334</v>
       </c>
       <c r="H75" t="n">
-        <v>160.89</v>
+        <v>163.04</v>
       </c>
       <c r="I75" t="n">
         <v>161.616137040274</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K75" t="n">
-        <v>1.82</v>
+        <v>0.51</v>
       </c>
       <c r="L75" t="n">
         <v>1.31</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>5.33</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>157.58</v>
+        <v>154.66</v>
       </c>
       <c r="I76" t="n">
         <v>154.9630094878762</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.35</v>
+        <v>-5.14</v>
       </c>
       <c r="L76" t="n">
-        <v>5.51</v>
+        <v>6.14</v>
       </c>
       <c r="M76" t="n">
         <v>1.2</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>6.92</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46062.55208333334</v>
+        <v>46063.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>164.02</v>
+        <v>164.55</v>
       </c>
       <c r="I77" t="n">
         <v>164.3228602577782</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.05</v>
+        <v>-6.39</v>
       </c>
       <c r="L77" t="n">
-        <v>6.19</v>
+        <v>8.06</v>
       </c>
       <c r="M77" t="n">
         <v>3.11</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>4.06</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>165.45</v>
+        <v>155.33</v>
       </c>
       <c r="I78" t="n">
         <v>163.0442065956988</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K78" t="n">
-        <v>0.55</v>
+        <v>-5.6</v>
       </c>
       <c r="L78" t="n">
-        <v>2.08</v>
+        <v>6.38</v>
       </c>
       <c r="M78" t="n">
-        <v>1.98</v>
+        <v>3.29</v>
       </c>
       <c r="N78" t="n">
-        <v>2.01</v>
+        <v>6.55</v>
       </c>
       <c r="O78" t="n">
         <v>0.17</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>7.87</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>145.18</v>
+        <v>153.35</v>
       </c>
       <c r="I79" t="n">
         <v>146.2361555551183</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K79" t="n">
-        <v>6.53</v>
+        <v>1.27</v>
       </c>
       <c r="L79" t="n">
         <v>3.35</v>
       </c>
       <c r="M79" t="n">
-        <v>2.77</v>
+        <v>5.19</v>
       </c>
       <c r="N79" t="n">
-        <v>3.15</v>
+        <v>5.73</v>
       </c>
       <c r="O79" t="n">
         <v>-6.55</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>6.9</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>162.14</v>
+        <v>159.19</v>
       </c>
       <c r="I80" t="n">
         <v>160.6432794319098</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K80" t="n">
-        <v>5.73</v>
+        <v>3.81</v>
       </c>
       <c r="L80" t="n">
         <v>3.16</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,25 +6008,25 @@
         <v>5.28</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>162.2</v>
+        <v>168.97</v>
       </c>
       <c r="I81" t="n">
         <v>162.5925360276089</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K81" t="n">
-        <v>-1.89</v>
+        <v>-6.14</v>
       </c>
       <c r="L81" t="n">
-        <v>2.2</v>
+        <v>7.23</v>
       </c>
       <c r="M81" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="N81" t="n">
         <v>4.11</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H82" t="n">
-        <v>174.48</v>
+        <v>168.9</v>
       </c>
       <c r="I82" t="n">
         <v>169.2728031641781</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K82" t="n">
-        <v>3.26</v>
+        <v>-0.04</v>
       </c>
       <c r="L82" t="n">
         <v>4.61</v>
@@ -5124,7 +6107,19 @@
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>5.95</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H83" t="n">
-        <v>173.75</v>
+        <v>177.31</v>
       </c>
       <c r="I83" t="n">
         <v>176.2165361650312</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K83" t="n">
-        <v>-2.87</v>
+        <v>-4.98</v>
       </c>
       <c r="L83" t="n">
-        <v>4.79</v>
+        <v>5.22</v>
       </c>
       <c r="M83" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N83" t="n">
-        <v>2.3</v>
+        <v>4.29</v>
       </c>
       <c r="O83" t="n">
         <v>-2.93</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,22 +6215,22 @@
         <v>5.06</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46241.55208333334</v>
+        <v>46244.38541666666</v>
       </c>
       <c r="H84" t="n">
-        <v>172.06</v>
+        <v>170.49</v>
       </c>
       <c r="I84" t="n">
         <v>171.2105434696578</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K84" t="n">
-        <v>-2.96</v>
+        <v>-3.85</v>
       </c>
       <c r="L84" t="n">
-        <v>3.06</v>
+        <v>4.11</v>
       </c>
       <c r="M84" t="n">
         <v>0.04</v>
@@ -5238,7 +6245,19 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>5.74</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H85" t="n">
-        <v>173</v>
+        <v>176.01</v>
       </c>
       <c r="I85" t="n">
         <v>175.8740438434563</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K85" t="n">
-        <v>-1.47</v>
+        <v>-3.24</v>
       </c>
       <c r="L85" t="n">
-        <v>3.41</v>
+        <v>3.99</v>
       </c>
       <c r="M85" t="n">
         <v>0.83</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,28 +6353,28 @@
         <v>3.89</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46296.55208333334</v>
+        <v>46300.38541666666</v>
       </c>
       <c r="H86" t="n">
-        <v>170.73</v>
+        <v>167.1</v>
       </c>
       <c r="I86" t="n">
         <v>169.8278984784453</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K86" t="n">
-        <v>-3</v>
+        <v>-5.06</v>
       </c>
       <c r="L86" t="n">
-        <v>4.31</v>
+        <v>5.44</v>
       </c>
       <c r="M86" t="n">
         <v>0.99</v>
       </c>
       <c r="N86" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="O86" t="n">
         <v>1.45</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,12 @@
       <c r="Q87" t="n">
         <v>32</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7505,7 +8554,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.3</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="6">
@@ -7515,7 +8564,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="7">
@@ -7525,7 +8574,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="8">
@@ -7535,7 +8584,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -7545,7 +8594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.2</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="10">
@@ -7555,7 +8604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36.3</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="11">
@@ -7565,7 +8614,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
@@ -7575,7 +8624,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -7585,7 +8634,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>81.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -7595,7 +8644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.77</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="15">
@@ -7605,7 +8654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.05</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="16">
@@ -7615,7 +8664,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.55</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="17">
@@ -7625,7 +8674,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.84</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="18">
@@ -7635,7 +8684,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.5</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="19">
@@ -7645,7 +8694,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.74</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="20">
@@ -7655,7 +8704,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.37</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="21">
@@ -7665,7 +8714,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.9</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="22">
@@ -7675,7 +8724,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -7685,7 +8734,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -7695,7 +8744,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="25">
@@ -7705,7 +8754,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.64</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -7715,7 +8764,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.83</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="27">
@@ -7725,7 +8774,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.01</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="28">
@@ -7735,7 +8784,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
